--- a/用卷/2025,2026.xlsx
+++ b/用卷/2025,2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AD6F0F-C168-4B6C-90D8-EA7E074F8666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C686B70-1448-4AA7-BD10-B10B49E60476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="181" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="96">
   <si>
     <t>年份</t>
   </si>
@@ -317,14 +317,18 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>英语听力不计入总成绩,笔试按阅读和七选五每题25'→3',完形1'→2',语法填空15'→2'折算为总成绩</t>
+    <t>2025和2026年普通高等学校招生全国统一考试用卷情况统计(语数英物化生政史地技)</t>
+  </si>
+  <si>
+    <t>2025和2026</t>
+  </si>
+  <si>
+    <t>语文、数学、英语为全国二卷,其他科目为陕晋青宁卷</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>2025和2026年普通高等学校招生全国统一考试用卷情况统计(语数英物化生政史地技)</t>
-  </si>
-  <si>
-    <t>2025和2026</t>
+    <t>英语听力不计入总成绩,笔试按阅读和七选五每题2.5'→3',完形1'→2',语法填空1.5'→2'折算为总成绩</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -509,6 +513,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -544,9 +551,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -882,6 +886,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D50"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -892,12 +899,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13"/>
+      <c r="A1" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -915,7 +922,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -929,7 +936,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
@@ -943,31 +950,31 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="17" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -979,21 +986,21 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
@@ -1005,7 +1012,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
@@ -1017,7 +1024,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
@@ -1029,7 +1036,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
@@ -1041,41 +1048,41 @@
     </row>
     <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="18"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="19"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="15"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="16"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>11</v>
@@ -1087,7 +1094,7 @@
     </row>
     <row r="17" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>52</v>
@@ -1095,13 +1102,13 @@
       <c r="C17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>53</v>
@@ -1109,11 +1116,11 @@
       <c r="C18" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="15"/>
+      <c r="D18" s="16"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>12</v>
@@ -1125,7 +1132,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>13</v>
@@ -1137,7 +1144,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>14</v>
@@ -1149,7 +1156,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>15</v>
@@ -1161,7 +1168,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>16</v>
@@ -1173,7 +1180,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>17</v>
@@ -1185,7 +1192,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>18</v>
@@ -1199,7 +1206,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>19</v>
@@ -1211,7 +1218,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>20</v>
@@ -1223,7 +1230,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>21</v>
@@ -1235,7 +1242,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>22</v>
@@ -1247,7 +1254,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>23</v>
@@ -1261,7 +1268,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>24</v>
@@ -1273,7 +1280,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>25</v>
@@ -1285,7 +1292,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>26</v>
@@ -1297,7 +1304,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>27</v>
@@ -1309,7 +1316,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>28</v>
@@ -1321,7 +1328,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>29</v>
@@ -1333,7 +1340,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>30</v>
@@ -1352,11 +1359,11 @@
       <c r="D38" s="7"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="11"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
@@ -1490,6 +1497,7 @@
     <mergeCell ref="C13:C15"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="75" fitToHeight="0" orientation="landscape" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>